--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>136858080</v>
       </c>
       <c r="B23" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>136858083</v>
       </c>
       <c r="B24" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>136858056</v>
       </c>
       <c r="B89" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>136858057</v>
       </c>
       <c r="B90" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>136858063</v>
       </c>
       <c r="B91" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>136858064</v>
       </c>
       <c r="B92" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>136858065</v>
       </c>
       <c r="B93" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136858070</v>
       </c>
       <c r="B94" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>136857938</v>
       </c>
       <c r="B137" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
